--- a/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC3/GradeDetail.xlsx
+++ b/batchstudent/1/AnhDThe187386/Results/AnhDThe187386/TC3/GradeDetail.xlsx
@@ -1056,7 +1056,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1115,7 +1115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>47</x:v>
@@ -1168,7 +1168,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1224,7 +1224,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1283,7 +1283,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>47</x:v>
@@ -1339,7 +1339,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>47</x:v>
@@ -1392,7 +1392,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1451,7 +1451,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>63</x:v>
@@ -1504,7 +1504,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1563,7 +1563,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>46754</x:v>
+        <x:v>58630</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>63</x:v>
@@ -1616,7 +1616,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q12" s="0">
         <x:v>4000</x:v>
@@ -1675,7 +1675,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R13" s="3" t="s">
         <x:v>63</x:v>
@@ -1728,7 +1728,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q14" s="0">
         <x:v>4000</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1843,7 +1843,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R16" s="3" t="s">
         <x:v>63</x:v>
@@ -1899,7 +1899,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
         <x:v>63</x:v>
@@ -1952,7 +1952,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P18" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q18" s="0">
         <x:v>4000</x:v>
@@ -2011,7 +2011,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>63</x:v>
@@ -2064,7 +2064,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="Q20" s="0">
         <x:v>4000</x:v>
@@ -2123,7 +2123,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>38232</x:v>
+        <x:v>54776</x:v>
       </x:c>
       <x:c r="R21" s="3" t="s">
         <x:v>63</x:v>
@@ -2176,7 +2176,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
@@ -2235,7 +2235,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q23" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
         <x:v>63</x:v>
@@ -2288,7 +2288,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P24" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q24" s="0">
         <x:v>4000</x:v>
@@ -2344,7 +2344,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P25" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q25" s="0">
         <x:v>4000</x:v>
@@ -2403,7 +2403,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q26" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R26" s="3" t="s">
         <x:v>63</x:v>
@@ -2459,7 +2459,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q27" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R27" s="3" t="s">
         <x:v>63</x:v>
@@ -2512,7 +2512,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P28" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q28" s="0">
         <x:v>4000</x:v>
@@ -2571,7 +2571,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q29" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R29" s="3" t="s">
         <x:v>63</x:v>
@@ -2624,7 +2624,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P30" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="Q30" s="0">
         <x:v>4000</x:v>
@@ -2683,7 +2683,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q31" s="0">
-        <x:v>45406</x:v>
+        <x:v>35268</x:v>
       </x:c>
       <x:c r="R31" s="3" t="s">
         <x:v>63</x:v>
